--- a/jogos_2025-07-07.xlsx
+++ b/jogos_2025-07-07.xlsx
@@ -885,10 +885,10 @@
         <v>2.25</v>
       </c>
       <c r="U2">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V2">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -897,10 +897,10 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AA2">
         <v>4.5</v>
@@ -912,22 +912,22 @@
         <v>2</v>
       </c>
       <c r="AD2">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AE2">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF2">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG2">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AH2">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="AI2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ2" t="s">
         <v>90</v>
@@ -936,13 +936,13 @@
         <v>90</v>
       </c>
       <c r="AL2">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AM2">
         <v>1.28</v>
       </c>
       <c r="AN2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -951,7 +951,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ2">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AR2">
         <v>1.56</v>
@@ -960,13 +960,13 @@
         <v>1.95</v>
       </c>
       <c r="AT2">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AU2">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AV2">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AW2">
         <v>2.21</v>
@@ -975,7 +975,7 @@
         <v>1.76</v>
       </c>
       <c r="AY2">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1389,37 +1389,37 @@
         <v>1.22</v>
       </c>
       <c r="S5">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V5">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Z5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AA5">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB5">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC5">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD5">
         <v>2.05</v>
@@ -1428,10 +1428,10 @@
         <v>1.65</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG5">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH5">
         <v>3.4</v>
@@ -1446,13 +1446,13 @@
         <v>90</v>
       </c>
       <c r="AL5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM5">
         <v>1.25</v>
       </c>
       <c r="AN5">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1461,16 +1461,16 @@
         <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AR5">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AS5">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AT5">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AU5">
         <v>7.17</v>
@@ -1479,10 +1479,10 @@
         <v>4.7</v>
       </c>
       <c r="AW5">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="AX5">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AY5">
         <v>1.86</v>
@@ -1586,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC6">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>1.57</v>
       </c>
       <c r="S7">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T7">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="U7">
         <v>1.25</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
         <v>5.75</v>
@@ -1762,22 +1762,22 @@
         <v>1.4</v>
       </c>
       <c r="AD7">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG7">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AH7">
         <v>10</v>
       </c>
       <c r="AI7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="s">
         <v>90</v>
@@ -1786,46 +1786,46 @@
         <v>90</v>
       </c>
       <c r="AL7">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AM7">
         <v>1.33</v>
       </c>
       <c r="AN7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AR7">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AS7">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AT7">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AU7">
         <v>3.8</v>
       </c>
       <c r="AV7">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AW7">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AX7">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AY7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1878,13 +1878,13 @@
         <v>89</v>
       </c>
       <c r="L8">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O8">
         <v>1.83</v>
@@ -1899,13 +1899,13 @@
         <v>1.59</v>
       </c>
       <c r="S8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1914,40 +1914,40 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="Z8">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AA8">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AB8">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AC8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AD8">
         <v>4.75</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AG8">
         <v>1.67</v>
       </c>
       <c r="AH8">
-        <v>9.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AI8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ8" t="s">
         <v>90</v>
@@ -1962,40 +1962,40 @@
         <v>1.31</v>
       </c>
       <c r="AN8">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
-        <v>1.38</v>
+        <v>2.11</v>
       </c>
       <c r="AS8">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="AT8">
-        <v>1.97</v>
+        <v>3.17</v>
       </c>
       <c r="AU8">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="AV8">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="AW8">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="AX8">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AY8">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2048,13 +2048,13 @@
         <v>89</v>
       </c>
       <c r="L9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M9">
         <v>3.1</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O9">
         <v>1.53</v>
@@ -2236,10 +2236,10 @@
         <v>3.5</v>
       </c>
       <c r="R10">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S10">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="T10">
         <v>3</v>
@@ -2254,16 +2254,16 @@
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y10">
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AA10">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB10">
         <v>2</v>
@@ -2272,22 +2272,22 @@
         <v>1.67</v>
       </c>
       <c r="AD10">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AE10">
         <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AH10">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AJ10" t="s">
         <v>90</v>
@@ -2296,25 +2296,25 @@
         <v>90</v>
       </c>
       <c r="AL10">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AM10">
         <v>1.27</v>
       </c>
       <c r="AN10">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AS10">
         <v>1.85</v>
@@ -2326,10 +2326,10 @@
         <v>4.33</v>
       </c>
       <c r="AV10">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AW10">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AX10">
         <v>1.85</v>

--- a/jogos_2025-07-07.xlsx
+++ b/jogos_2025-07-07.xlsx
@@ -876,22 +876,22 @@
         <v>1.62</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="T2">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="U2">
         <v>1.57</v>
       </c>
       <c r="V2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -900,10 +900,10 @@
         <v>15</v>
       </c>
       <c r="Z2">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AB2">
         <v>1.65</v>
@@ -918,16 +918,16 @@
         <v>1.62</v>
       </c>
       <c r="AF2">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG2">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH2">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AI2">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ2" t="s">
         <v>90</v>
@@ -936,19 +936,19 @@
         <v>90</v>
       </c>
       <c r="AL2">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AM2">
         <v>1.28</v>
       </c>
       <c r="AN2">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AO2">
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
         <v>1.3</v>
@@ -957,25 +957,25 @@
         <v>1.56</v>
       </c>
       <c r="AS2">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AT2">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AU2">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AV2">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="AW2">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AX2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AY2">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1368,13 +1368,13 @@
         <v>89</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M5">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O5">
         <v>1.67</v>
@@ -1386,40 +1386,40 @@
         <v>2.17</v>
       </c>
       <c r="R5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S5">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T5">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="U5">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V5">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>19</v>
       </c>
       <c r="Z5">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AA5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AB5">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC5">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AD5">
         <v>2.05</v>
@@ -1428,16 +1428,16 @@
         <v>1.65</v>
       </c>
       <c r="AF5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH5">
         <v>3.4</v>
       </c>
       <c r="AI5">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ5" t="s">
         <v>90</v>
@@ -1446,13 +1446,13 @@
         <v>90</v>
       </c>
       <c r="AL5">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AM5">
         <v>1.25</v>
       </c>
       <c r="AN5">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1461,31 +1461,31 @@
         <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AR5">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AS5">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AT5">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AU5">
         <v>7.17</v>
       </c>
       <c r="AV5">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="AW5">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AX5">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AY5">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1586,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC6">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1726,28 +1726,28 @@
         <v>3.5</v>
       </c>
       <c r="R7">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S7">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="T7">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="U7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V7">
         <v>11</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y7">
-        <v>5.75</v>
+        <v>6.45</v>
       </c>
       <c r="Z7">
         <v>1.5</v>
@@ -1756,28 +1756,28 @@
         <v>2.3</v>
       </c>
       <c r="AB7">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AC7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AD7">
         <v>5.8</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG7">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AH7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AI7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ7" t="s">
         <v>90</v>
@@ -1786,46 +1786,46 @@
         <v>90</v>
       </c>
       <c r="AL7">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AM7">
         <v>1.33</v>
       </c>
       <c r="AN7">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AQ7">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AS7">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AT7">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="AU7">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV7">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AW7">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AX7">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AY7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1878,13 +1878,13 @@
         <v>89</v>
       </c>
       <c r="L8">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="M8">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="N8">
-        <v>2.95</v>
+        <v>3.23</v>
       </c>
       <c r="O8">
         <v>1.83</v>
@@ -1896,16 +1896,16 @@
         <v>2.4</v>
       </c>
       <c r="R8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S8">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1914,40 +1914,40 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y8">
-        <v>6.05</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>1.49</v>
       </c>
       <c r="AA8">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB8">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="AC8">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AD8">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH8">
-        <v>11.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="s">
         <v>90</v>
@@ -1956,46 +1956,46 @@
         <v>90</v>
       </c>
       <c r="AL8">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AM8">
         <v>1.31</v>
       </c>
       <c r="AN8">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AR8">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AS8">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AT8">
-        <v>3.17</v>
+        <v>2</v>
       </c>
       <c r="AU8">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="AV8">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
       <c r="AW8">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AX8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AY8">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2048,13 +2048,13 @@
         <v>89</v>
       </c>
       <c r="L9">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="M9">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
         <v>1.53</v>
@@ -2090,16 +2090,16 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AA9">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AB9">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AC9">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2236,16 +2236,16 @@
         <v>3.5</v>
       </c>
       <c r="R10">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S10">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V10">
         <v>7.5</v>
@@ -2257,13 +2257,13 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z10">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AA10">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB10">
         <v>2</v>
@@ -2272,19 +2272,19 @@
         <v>1.67</v>
       </c>
       <c r="AD10">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AG10">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI10">
         <v>1.07</v>
@@ -2296,13 +2296,13 @@
         <v>90</v>
       </c>
       <c r="AL10">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AM10">
         <v>1.27</v>
       </c>
       <c r="AN10">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2311,31 +2311,31 @@
         <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AR10">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AS10">
         <v>1.85</v>
       </c>
       <c r="AT10">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AU10">
         <v>4.33</v>
       </c>
       <c r="AV10">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AW10">
         <v>2.3</v>
       </c>
       <c r="AX10">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AY10">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AZ10">
         <v>0</v>

--- a/jogos_2025-07-07.xlsx
+++ b/jogos_2025-07-07.xlsx
@@ -247,12 +247,12 @@
     <t>Operário PR</t>
   </si>
   <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
     <t>América Mineiro</t>
   </si>
   <si>
@@ -274,10 +274,10 @@
     <t>Chapecoense</t>
   </si>
   <si>
+    <t>Tombense</t>
+  </si>
+  <si>
     <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Tombense</t>
   </si>
   <si>
     <t>Athletic Club</t>
@@ -876,22 +876,22 @@
         <v>1.62</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="T2">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U2">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V2">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -900,7 +900,7 @@
         <v>15</v>
       </c>
       <c r="Z2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA2">
         <v>4.8</v>
@@ -918,16 +918,16 @@
         <v>1.62</v>
       </c>
       <c r="AF2">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG2">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH2">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="AI2">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>90</v>
@@ -936,46 +936,46 @@
         <v>90</v>
       </c>
       <c r="AL2">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="AM2">
         <v>1.28</v>
       </c>
       <c r="AN2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO2">
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AQ2">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR2">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AS2">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AT2">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AU2">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AV2">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AW2">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AX2">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AY2">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1028,76 +1028,76 @@
         <v>89</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ3" t="s">
         <v>90</v>
@@ -1106,13 +1106,13 @@
         <v>90</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AM3">
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BD3" s="3">
         <v>45845.5</v>
@@ -1386,13 +1386,13 @@
         <v>2.17</v>
       </c>
       <c r="R5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T5">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="U5">
         <v>1.7</v>
@@ -1404,16 +1404,16 @@
         <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>19</v>
       </c>
       <c r="Z5">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AA5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AB5">
         <v>1.42</v>
@@ -1428,7 +1428,7 @@
         <v>1.65</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG5">
         <v>2.7</v>
@@ -1437,7 +1437,7 @@
         <v>3.4</v>
       </c>
       <c r="AI5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AJ5" t="s">
         <v>90</v>
@@ -1446,46 +1446,46 @@
         <v>90</v>
       </c>
       <c r="AL5">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AM5">
         <v>1.25</v>
       </c>
       <c r="AN5">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ5">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR5">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AS5">
         <v>1.52</v>
       </c>
       <c r="AT5">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AU5">
-        <v>7.17</v>
+        <v>5.75</v>
       </c>
       <c r="AV5">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AW5">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AX5">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AY5">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1547,43 +1547,43 @@
         <v>4.4</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB6">
         <v>2.43</v>
@@ -1592,22 +1592,22 @@
         <v>1.52</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ6" t="s">
         <v>90</v>
@@ -1616,46 +1616,46 @@
         <v>90</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM6">
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" s="3">
         <v>45845.77083333334</v>
@@ -1726,28 +1726,28 @@
         <v>3.5</v>
       </c>
       <c r="R7">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S7">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="T7">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>1.5</v>
@@ -1762,10 +1762,10 @@
         <v>1.41</v>
       </c>
       <c r="AD7">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
         <v>2.3</v>
@@ -1774,10 +1774,10 @@
         <v>1.57</v>
       </c>
       <c r="AH7">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AI7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="s">
         <v>90</v>
@@ -1786,46 +1786,46 @@
         <v>90</v>
       </c>
       <c r="AL7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AM7">
         <v>1.33</v>
       </c>
       <c r="AN7">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS7">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AT7">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AU7">
         <v>4.2</v>
       </c>
       <c r="AV7">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AW7">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AX7">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AY7">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1878,34 +1878,34 @@
         <v>89</v>
       </c>
       <c r="L8">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="M8">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="N8">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S8">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T8">
-        <v>3.52</v>
+        <v>3.72</v>
       </c>
       <c r="U8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1914,37 +1914,37 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="Z8">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AA8">
+        <v>2.27</v>
+      </c>
+      <c r="AB8">
+        <v>2.65</v>
+      </c>
+      <c r="AC8">
+        <v>1.42</v>
+      </c>
+      <c r="AD8">
+        <v>5.25</v>
+      </c>
+      <c r="AE8">
+        <v>1.12</v>
+      </c>
+      <c r="AF8">
         <v>2.3</v>
       </c>
-      <c r="AB8">
-        <v>2.69</v>
-      </c>
-      <c r="AC8">
-        <v>1.41</v>
-      </c>
-      <c r="AD8">
-        <v>4.9</v>
-      </c>
-      <c r="AE8">
-        <v>1.15</v>
-      </c>
-      <c r="AF8">
-        <v>2.08</v>
-      </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH8">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AI8">
         <v>1.02</v>
@@ -1956,46 +1956,46 @@
         <v>90</v>
       </c>
       <c r="AL8">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AM8">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AQ8">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AR8">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AS8">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AT8">
-        <v>2</v>
+        <v>3.48</v>
       </c>
       <c r="AU8">
-        <v>4.9</v>
+        <v>3.04</v>
       </c>
       <c r="AV8">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="AW8">
         <v>1.87</v>
       </c>
       <c r="AX8">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AY8">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="BC8">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="BD8" s="3">
         <v>45845.8125</v>
@@ -2048,76 +2048,76 @@
         <v>89</v>
       </c>
       <c r="L9">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="M9">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="N9">
+        <v>3.23</v>
+      </c>
+      <c r="O9">
+        <v>1.83</v>
+      </c>
+      <c r="P9">
+        <v>6.15</v>
+      </c>
+      <c r="Q9">
+        <v>2.4</v>
+      </c>
+      <c r="R9">
+        <v>1.65</v>
+      </c>
+      <c r="S9">
+        <v>2.1</v>
+      </c>
+      <c r="T9">
         <v>4.1</v>
       </c>
-      <c r="O9">
-        <v>1.53</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>3.4</v>
-      </c>
-      <c r="R9">
-        <v>1.53</v>
-      </c>
-      <c r="S9">
-        <v>2.38</v>
-      </c>
-      <c r="T9">
-        <v>3.75</v>
-      </c>
       <c r="U9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V9">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z9">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AA9">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AB9">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="AC9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
         <v>90</v>
@@ -2126,46 +2126,46 @@
         <v>90</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="BC9">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="BD9" s="3">
         <v>45845.8125</v>
@@ -2236,34 +2236,34 @@
         <v>3.5</v>
       </c>
       <c r="R10">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V10">
+        <v>8.9</v>
+      </c>
+      <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.07</v>
+      </c>
+      <c r="Y10">
         <v>7.5</v>
       </c>
-      <c r="W10">
-        <v>1.06</v>
-      </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
-        <v>9.300000000000001</v>
-      </c>
       <c r="Z10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AA10">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="AB10">
         <v>2</v>
@@ -2272,22 +2272,22 @@
         <v>1.67</v>
       </c>
       <c r="AD10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AE10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI10">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
         <v>90</v>
@@ -2296,46 +2296,46 @@
         <v>90</v>
       </c>
       <c r="AL10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AM10">
         <v>1.27</v>
       </c>
       <c r="AN10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AQ10">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR10">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AS10">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AT10">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AU10">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AV10">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AW10">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AX10">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AY10">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AZ10">
         <v>0</v>

--- a/jogos_2025-07-07.xlsx
+++ b/jogos_2025-07-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -283,10 +229,40 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['11', '69']</t>
+  </si>
+  <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['67', '90+9']</t>
+  </si>
+  <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['17']</t>
   </si>
 </sst>
 </file>
@@ -650,10 +626,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -768,94 +744,40 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45845</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
         <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>89</v>
       </c>
       <c r="L2">
         <v>3.09</v>
@@ -876,34 +798,34 @@
         <v>1.62</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="W2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AA2">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AB2">
         <v>1.65</v>
@@ -918,174 +840,120 @@
         <v>1.62</v>
       </c>
       <c r="AF2">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG2">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AH2">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AI2">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="AK2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL2">
-        <v>1.26</v>
-      </c>
-      <c r="AM2">
-        <v>1.28</v>
-      </c>
-      <c r="AN2">
-        <v>1.33</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.17</v>
-      </c>
-      <c r="AQ2">
-        <v>1.35</v>
-      </c>
-      <c r="AR2">
-        <v>1.55</v>
-      </c>
-      <c r="AS2">
-        <v>1.94</v>
-      </c>
-      <c r="AT2">
-        <v>2.4</v>
-      </c>
-      <c r="AU2">
-        <v>3.95</v>
-      </c>
-      <c r="AV2">
-        <v>2.9</v>
-      </c>
-      <c r="AW2">
-        <v>2.23</v>
-      </c>
-      <c r="AX2">
-        <v>1.77</v>
-      </c>
-      <c r="AY2">
-        <v>1.5</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2.3</v>
-      </c>
-      <c r="BC2">
-        <v>1.62</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45845.5</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45845</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L3">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="M3">
-        <v>4.5</v>
+        <v>5.17</v>
       </c>
       <c r="N3">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="O3">
         <v>1.25</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q3">
         <v>4.75</v>
       </c>
       <c r="R3">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T3">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="U3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V3">
-        <v>6</v>
+        <v>7.02</v>
       </c>
       <c r="W3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
         <v>10</v>
       </c>
       <c r="Z3">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AA3">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AC3">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD3">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AE3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF3">
         <v>2.28</v>
@@ -1094,99 +962,45 @@
         <v>1.59</v>
       </c>
       <c r="AH3">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AI3">
         <v>1.11</v>
       </c>
       <c r="AJ3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="AK3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL3">
-        <v>1.17</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>3.2</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.25</v>
-      </c>
-      <c r="BC3">
-        <v>4.75</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>72</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45845.5</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45845</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1195,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L4">
         <v>2.37</v>
@@ -1270,111 +1084,57 @@
         <v>1.25</v>
       </c>
       <c r="AJ4" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="AK4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL4">
-        <v>1.48</v>
-      </c>
-      <c r="AM4">
-        <v>1.22</v>
-      </c>
-      <c r="AN4">
-        <v>1.5</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.13</v>
-      </c>
-      <c r="AQ4">
-        <v>1.24</v>
-      </c>
-      <c r="AR4">
-        <v>1.41</v>
-      </c>
-      <c r="AS4">
-        <v>1.66</v>
-      </c>
-      <c r="AT4">
-        <v>1.98</v>
-      </c>
-      <c r="AU4">
-        <v>4.9</v>
-      </c>
-      <c r="AV4">
-        <v>3.55</v>
-      </c>
-      <c r="AW4">
-        <v>2.65</v>
-      </c>
-      <c r="AX4">
-        <v>2.08</v>
-      </c>
-      <c r="AY4">
-        <v>1.72</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.8</v>
-      </c>
-      <c r="BC4">
-        <v>2</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>78</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45845.58333333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45845</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L5">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="N5">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="O5">
         <v>1.67</v>
@@ -1389,332 +1149,224 @@
         <v>1.22</v>
       </c>
       <c r="S5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U5">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="V5">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Z5">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AA5">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AB5">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AC5">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD5">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE5">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF5">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AI5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL5">
-        <v>1.21</v>
-      </c>
-      <c r="AM5">
-        <v>1.25</v>
-      </c>
-      <c r="AN5">
-        <v>1.7</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.1</v>
-      </c>
-      <c r="AQ5">
-        <v>1.13</v>
-      </c>
-      <c r="AR5">
-        <v>1.27</v>
-      </c>
-      <c r="AS5">
-        <v>1.52</v>
-      </c>
-      <c r="AT5">
-        <v>1.86</v>
-      </c>
-      <c r="AU5">
-        <v>5.75</v>
-      </c>
-      <c r="AV5">
-        <v>4.55</v>
-      </c>
-      <c r="AW5">
-        <v>3.14</v>
-      </c>
-      <c r="AX5">
-        <v>2.3</v>
-      </c>
-      <c r="AY5">
-        <v>1.86</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.67</v>
-      </c>
-      <c r="BC5">
-        <v>2.17</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>79</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45845.67708333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45845</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L6">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="M6">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>1.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>3.25</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S6">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V6">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AA6">
+        <v>2.43</v>
+      </c>
+      <c r="AB6">
         <v>2.6</v>
       </c>
-      <c r="AB6">
-        <v>2.43</v>
-      </c>
       <c r="AC6">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AD6">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AE6">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG6">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH6">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AI6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ6" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL6">
-        <v>1.3</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>2.15</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>1.56</v>
-      </c>
-      <c r="AQ6">
-        <v>2.02</v>
-      </c>
-      <c r="AR6">
-        <v>3.38</v>
-      </c>
-      <c r="AS6">
-        <v>3.4</v>
-      </c>
-      <c r="AT6">
-        <v>4.75</v>
-      </c>
-      <c r="AU6">
-        <v>2.2</v>
-      </c>
-      <c r="AV6">
-        <v>1.73</v>
-      </c>
-      <c r="AW6">
-        <v>1.44</v>
-      </c>
-      <c r="AX6">
-        <v>1.29</v>
-      </c>
-      <c r="AY6">
-        <v>1.14</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.5</v>
-      </c>
-      <c r="BC6">
-        <v>3.25</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>72</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45845.77083333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45845</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L7">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="M7">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="O7">
         <v>1.53</v>
@@ -1726,7 +1378,7 @@
         <v>3.5</v>
       </c>
       <c r="R7">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="S7">
         <v>2.25</v>
@@ -1735,135 +1387,81 @@
         <v>3.9</v>
       </c>
       <c r="U7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="Z7">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA7">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AB7">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AC7">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AD7">
-        <v>5.25</v>
+        <v>6.2</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AG7">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH7">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AI7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ7" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="AK7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL7">
-        <v>1.36</v>
-      </c>
-      <c r="AM7">
-        <v>1.33</v>
-      </c>
-      <c r="AN7">
-        <v>1.95</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.22</v>
-      </c>
-      <c r="AQ7">
-        <v>1.36</v>
-      </c>
-      <c r="AR7">
-        <v>1.62</v>
-      </c>
-      <c r="AS7">
-        <v>2.15</v>
-      </c>
-      <c r="AT7">
-        <v>2.75</v>
-      </c>
-      <c r="AU7">
-        <v>4.2</v>
-      </c>
-      <c r="AV7">
-        <v>2.88</v>
-      </c>
-      <c r="AW7">
-        <v>2</v>
-      </c>
-      <c r="AX7">
-        <v>1.75</v>
-      </c>
-      <c r="AY7">
-        <v>1.35</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.53</v>
-      </c>
-      <c r="BC7">
-        <v>3.5</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>80</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45845.79166666666</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45845</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1875,168 +1473,114 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L8">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M8">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>4.95</v>
       </c>
       <c r="O8">
         <v>1.53</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
       </c>
       <c r="R8">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S8">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T8">
-        <v>3.72</v>
+        <v>4.33</v>
       </c>
       <c r="U8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
+        <v>1.15</v>
+      </c>
+      <c r="Y8">
+        <v>5.25</v>
+      </c>
+      <c r="Z8">
+        <v>1.66</v>
+      </c>
+      <c r="AA8">
+        <v>2.1</v>
+      </c>
+      <c r="AB8">
+        <v>2.9</v>
+      </c>
+      <c r="AC8">
+        <v>1.36</v>
+      </c>
+      <c r="AD8">
+        <v>5.9</v>
+      </c>
+      <c r="AE8">
         <v>1.1</v>
       </c>
-      <c r="Y8">
-        <v>5.75</v>
-      </c>
-      <c r="Z8">
-        <v>1.56</v>
-      </c>
-      <c r="AA8">
-        <v>2.27</v>
-      </c>
-      <c r="AB8">
+      <c r="AF8">
         <v>2.65</v>
       </c>
-      <c r="AC8">
-        <v>1.42</v>
-      </c>
-      <c r="AD8">
-        <v>5.25</v>
-      </c>
-      <c r="AE8">
-        <v>1.12</v>
-      </c>
-      <c r="AF8">
-        <v>2.3</v>
-      </c>
       <c r="AG8">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH8">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AI8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ8" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL8">
-        <v>1.38</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>1.8</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>1.29</v>
-      </c>
-      <c r="AQ8">
-        <v>1.58</v>
-      </c>
-      <c r="AR8">
-        <v>2.27</v>
-      </c>
-      <c r="AS8">
-        <v>2.53</v>
-      </c>
-      <c r="AT8">
-        <v>3.48</v>
-      </c>
-      <c r="AU8">
-        <v>3.04</v>
-      </c>
-      <c r="AV8">
-        <v>2.34</v>
-      </c>
-      <c r="AW8">
-        <v>1.87</v>
-      </c>
-      <c r="AX8">
-        <v>1.43</v>
-      </c>
-      <c r="AY8">
-        <v>1.22</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.53</v>
-      </c>
-      <c r="BC8">
-        <v>3.4</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>72</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45845.8125</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45845</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
         <v>69</v>
       </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" t="s">
-        <v>87</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2045,16 +1589,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L9">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="M9">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="N9">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="O9">
         <v>1.83</v>
@@ -2066,165 +1610,111 @@
         <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="S9">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="T9">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U9">
         <v>1.22</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y9">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Z9">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AA9">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB9">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AC9">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AD9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG9">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AK9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL9">
-        <v>1.37</v>
-      </c>
-      <c r="AM9">
-        <v>1.31</v>
-      </c>
-      <c r="AN9">
-        <v>1.42</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>1.22</v>
-      </c>
-      <c r="AQ9">
-        <v>1.38</v>
-      </c>
-      <c r="AR9">
-        <v>1.65</v>
-      </c>
-      <c r="AS9">
-        <v>2.21</v>
-      </c>
-      <c r="AT9">
-        <v>2.91</v>
-      </c>
-      <c r="AU9">
-        <v>3.8</v>
-      </c>
-      <c r="AV9">
-        <v>2.8</v>
-      </c>
-      <c r="AW9">
-        <v>2.1</v>
-      </c>
-      <c r="AX9">
-        <v>1.73</v>
-      </c>
-      <c r="AY9">
-        <v>1.48</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.83</v>
-      </c>
-      <c r="BC9">
-        <v>2.4</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>81</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45845.8125</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45845</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
         <v>70</v>
       </c>
-      <c r="E10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" t="s">
-        <v>88</v>
-      </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="M10">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N10">
-        <v>5.3</v>
+        <v>4.85</v>
       </c>
       <c r="O10">
         <v>1.4</v>
@@ -2236,120 +1726,66 @@
         <v>3.5</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S10">
+        <v>2.45</v>
+      </c>
+      <c r="T10">
+        <v>3.2</v>
+      </c>
+      <c r="U10">
+        <v>1.3</v>
+      </c>
+      <c r="V10">
+        <v>8.5</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1.06</v>
+      </c>
+      <c r="Y10">
+        <v>7.2</v>
+      </c>
+      <c r="Z10">
+        <v>1.39</v>
+      </c>
+      <c r="AA10">
         <v>2.6</v>
       </c>
-      <c r="T10">
-        <v>3</v>
-      </c>
-      <c r="U10">
-        <v>1.33</v>
-      </c>
-      <c r="V10">
-        <v>8.9</v>
-      </c>
-      <c r="W10">
-        <v>1.05</v>
-      </c>
-      <c r="X10">
-        <v>1.07</v>
-      </c>
-      <c r="Y10">
-        <v>7.5</v>
-      </c>
-      <c r="Z10">
-        <v>1.38</v>
-      </c>
-      <c r="AA10">
-        <v>3.06</v>
-      </c>
       <c r="AB10">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC10">
+        <v>1.5</v>
+      </c>
+      <c r="AD10">
+        <v>4.4</v>
+      </c>
+      <c r="AE10">
+        <v>1.14</v>
+      </c>
+      <c r="AF10">
+        <v>1.97</v>
+      </c>
+      <c r="AG10">
         <v>1.67</v>
       </c>
-      <c r="AD10">
-        <v>4.2</v>
-      </c>
-      <c r="AE10">
-        <v>1.22</v>
-      </c>
-      <c r="AF10">
-        <v>2.05</v>
-      </c>
-      <c r="AG10">
-        <v>1.7</v>
-      </c>
       <c r="AH10">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="AI10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="AK10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL10">
-        <v>1.3</v>
-      </c>
-      <c r="AM10">
-        <v>1.27</v>
-      </c>
-      <c r="AN10">
-        <v>2.15</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>1.15</v>
-      </c>
-      <c r="AQ10">
-        <v>1.29</v>
-      </c>
-      <c r="AR10">
-        <v>1.5</v>
-      </c>
-      <c r="AS10">
-        <v>1.75</v>
-      </c>
-      <c r="AT10">
-        <v>2.2</v>
-      </c>
-      <c r="AU10">
-        <v>4.75</v>
-      </c>
-      <c r="AV10">
-        <v>3.3</v>
-      </c>
-      <c r="AW10">
-        <v>2.4</v>
-      </c>
-      <c r="AX10">
-        <v>1.95</v>
-      </c>
-      <c r="AY10">
-        <v>1.5</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.4</v>
-      </c>
-      <c r="BC10">
-        <v>3.5</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>82</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45845.875</v>
       </c>
     </row>

--- a/jogos_2025-07-07.xlsx
+++ b/jogos_2025-07-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,22 +643,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.09</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.39</v>
+        <v>5.17</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>3.43</v>
+        <v>1.79</v>
       </c>
       <c r="P2" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>['11', '69']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG2" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.62</v>
+        <v>4.75</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45845.5</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>3.09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.17</v>
+        <v>3.39</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.79</v>
+        <v>3.43</v>
       </c>
       <c r="P3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>9.5</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>2.85</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.4</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AD3" t="n">
-        <v>1.59</v>
+        <v>2.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['11', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.13</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45845.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.07</v>
+        <v>1.74</v>
       </c>
       <c r="M9" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>23</v>
+        <v>4.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>6.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>2.32</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>2.88</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>1.38</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['21', '45+4', '72', '90+4']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67', '90+9']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45845.79166666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>1.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.85</v>
+        <v>23</v>
       </c>
       <c r="O10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.45</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['21', '45+4', '72', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['67', '90+9']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2</v>
-      </c>
       <c r="AI10" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45845.79166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>4.8</v>
+        <v>2.73</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.55</v>
+        <v>4.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="AC13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['54', '90+1']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45845.875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.5</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>2.73</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.63</v>
+        <v>2.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD15" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD15" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['54', '90+1']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45845.875</v>
